--- a/e2e-web/reports/selenium-report.xlsx
+++ b/e2e-web/reports/selenium-report.xlsx
@@ -128,19 +128,19 @@
     <t>Run Started (UTC)</t>
   </si>
   <si>
-    <t>2026-09-04T05:10:30.939Z</t>
+    <t>2026-09-04T05:36:14.456Z</t>
   </si>
   <si>
     <t>Run Ended (UTC)</t>
   </si>
   <si>
-    <t>2026-09-04T05:12:16.815Z</t>
+    <t>2026-09-04T05:37:05.874Z</t>
   </si>
   <si>
     <t>Report Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-09-04T05:12:16.816Z</t>
+    <t>2026-09-04T05:37:05.875Z</t>
   </si>
 </sst>
 </file>
@@ -560,7 +560,7 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -574,7 +574,7 @@
         <v>6</v>
       </c>
       <c r="D3">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -588,7 +588,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>187</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -602,7 +602,7 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>653</v>
+        <v>555</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -616,7 +616,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>176</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -630,7 +630,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>145</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -644,7 +644,7 @@
         <v>6</v>
       </c>
       <c r="D8">
-        <v>136</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -658,7 +658,7 @@
         <v>6</v>
       </c>
       <c r="D9">
-        <v>112</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -672,7 +672,7 @@
         <v>6</v>
       </c>
       <c r="D10">
-        <v>1249</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -686,7 +686,7 @@
         <v>6</v>
       </c>
       <c r="D11">
-        <v>6308</v>
+        <v>6379</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -700,7 +700,7 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>168</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -714,7 +714,7 @@
         <v>6</v>
       </c>
       <c r="D13">
-        <v>400</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -728,7 +728,7 @@
         <v>6</v>
       </c>
       <c r="D14">
-        <v>350</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -742,7 +742,7 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>373</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -756,7 +756,7 @@
         <v>6</v>
       </c>
       <c r="D16">
-        <v>539</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -820,7 +820,7 @@
         <v>34</v>
       </c>
       <c r="B6">
-        <v>10920</v>
+        <v>10496</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -828,7 +828,7 @@
         <v>35</v>
       </c>
       <c r="B7">
-        <v>105876</v>
+        <v>51418</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">

--- a/e2e-web/reports/selenium-report.xlsx
+++ b/e2e-web/reports/selenium-report.xlsx
@@ -128,19 +128,19 @@
     <t>Run Started (UTC)</t>
   </si>
   <si>
-    <t>2026-09-04T05:36:14.456Z</t>
+    <t>2026-09-04T07:16:54.367Z</t>
   </si>
   <si>
     <t>Run Ended (UTC)</t>
   </si>
   <si>
-    <t>2026-09-04T05:37:05.874Z</t>
+    <t>2026-09-04T07:17:25.027Z</t>
   </si>
   <si>
     <t>Report Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-09-04T05:37:05.875Z</t>
+    <t>2026-09-04T07:17:25.028Z</t>
   </si>
 </sst>
 </file>
@@ -560,7 +560,7 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -574,7 +574,7 @@
         <v>6</v>
       </c>
       <c r="D3">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -588,7 +588,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>151</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -602,7 +602,7 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>555</v>
+        <v>626</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -616,7 +616,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -630,7 +630,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>107</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -644,7 +644,7 @@
         <v>6</v>
       </c>
       <c r="D8">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -658,7 +658,7 @@
         <v>6</v>
       </c>
       <c r="D9">
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -672,7 +672,7 @@
         <v>6</v>
       </c>
       <c r="D10">
-        <v>1215</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -686,7 +686,7 @@
         <v>6</v>
       </c>
       <c r="D11">
-        <v>6379</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -700,7 +700,7 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>225</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -714,7 +714,7 @@
         <v>6</v>
       </c>
       <c r="D13">
-        <v>293</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -728,7 +728,7 @@
         <v>6</v>
       </c>
       <c r="D14">
-        <v>376</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -742,7 +742,7 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>264</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -756,7 +756,7 @@
         <v>6</v>
       </c>
       <c r="D16">
-        <v>490</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -820,7 +820,7 @@
         <v>34</v>
       </c>
       <c r="B6">
-        <v>10496</v>
+        <v>9646</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -828,7 +828,7 @@
         <v>35</v>
       </c>
       <c r="B7">
-        <v>51418</v>
+        <v>30660</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">

--- a/e2e-web/reports/selenium-report.xlsx
+++ b/e2e-web/reports/selenium-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="47">
   <si>
     <t>Test Name</t>
   </si>
@@ -98,6 +98,21 @@
     <t>Responsive mobile nav</t>
   </si>
   <si>
+    <t>does not expose common secret markers in the page source</t>
+  </si>
+  <si>
+    <t>Security smoke checks</t>
+  </si>
+  <si>
+    <t>uses password controls and no insecure external resources</t>
+  </si>
+  <si>
+    <t>calculates totals, durations, and pass rate from test results</t>
+  </si>
+  <si>
+    <t>Report model unit tests</t>
+  </si>
+  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -128,19 +143,16 @@
     <t>Run Started (UTC)</t>
   </si>
   <si>
-    <t>2026-09-04T07:16:54.367Z</t>
+    <t>2026-09-04T18:22:26.068Z</t>
   </si>
   <si>
     <t>Run Ended (UTC)</t>
   </si>
   <si>
-    <t>2026-09-04T07:17:25.027Z</t>
+    <t>2026-09-04T18:22:46.858Z</t>
   </si>
   <si>
     <t>Report Generated (UTC)</t>
-  </si>
-  <si>
-    <t>2026-09-04T07:17:25.028Z</t>
   </si>
 </sst>
 </file>
@@ -526,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -560,7 +572,7 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -574,7 +586,7 @@
         <v>6</v>
       </c>
       <c r="D3">
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -588,7 +600,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>187</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -602,7 +614,7 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>626</v>
+        <v>556</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -616,7 +628,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -630,7 +642,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -644,7 +656,7 @@
         <v>6</v>
       </c>
       <c r="D8">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -658,7 +670,7 @@
         <v>6</v>
       </c>
       <c r="D9">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -672,7 +684,7 @@
         <v>6</v>
       </c>
       <c r="D10">
-        <v>1118</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -686,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="D11">
-        <v>6275</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -700,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -714,7 +726,7 @@
         <v>6</v>
       </c>
       <c r="D13">
-        <v>199</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -728,7 +740,7 @@
         <v>6</v>
       </c>
       <c r="D14">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -742,7 +754,7 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>283</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -756,7 +768,49 @@
         <v>6</v>
       </c>
       <c r="D16">
-        <v>126</v>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -777,31 +831,31 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -809,7 +863,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -817,23 +871,23 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B6">
-        <v>9646</v>
+        <v>10057</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B7">
-        <v>30660</v>
+        <v>20790</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -841,26 +895,26 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
